--- a/TheSnackChoice_OperatingSystem.xlsx
+++ b/TheSnackChoice_OperatingSystem.xlsx
@@ -14,8 +14,9 @@
     <sheet name="Playbooks" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Decision Policies" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Machines" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Risk Register" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Assumptions &amp; Spikes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Planograms" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Risk Register" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Assumptions &amp; Spikes" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -694,6 +695,216 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Assumptions &amp; Spikes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Evidence or spike. SPIKE rows have an experiment in scratch/spikes/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Spike</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Unblocks</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>spike.001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Restock fill-level trigger threshold</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>config/policies.yaml#restock-trigger, tools/route.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>spike.002</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Default restock cadence per machine</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>config/cadence.yaml, config/workflows.yaml#weekly-route</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>spike.003</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Stockout-rate target</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>config/kpis.yaml#stockout_rate_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>spike.004</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cash variance tolerance</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>config/kpis.yaml#cash_variance_pct, config/policies.yaml#cash-investigate</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>spike.005</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Product add/cut rule</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>config/policies.yaml#product-cut</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>spike.006</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Target vends/day and machine-buy trigger</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>config/kpis.yaml#vends_per_machine_per_day, config/policies.yaml#machine-buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>spike.007</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Planogram par levels per facing</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>config/planograms.yaml, tools/reorder.py</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2028,6 +2239,1537 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Planograms</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Slot → SKU → par plan per machine. reorder.py refills to par. Par levels: spike 007.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Planogram</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Facings</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Par/facing</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>standard-industrial (48 sel, 362 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mars Bar 51g</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Snickers 48g</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KitKat 4 Finger 41.5g</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dairy Milk 45g</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Twirl 43g</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Maltesers 37g</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kinder Bueno 43g</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bounty 57g</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Skittles Fruits 45g</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Haribo Starmix 40g</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Walkers Cheese &amp; Onion Grab Bag 45g</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Crisps</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Walkers Ready Salted Grab Bag 45g</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Crisps</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>McCoy's Salt &amp; Vinegar Grab Bag 45g</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Crisps</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Doritos Chilli Heatwave 40g</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Crisps</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Quavers Cheese 34g</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Crisps</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Wotsits Really Cheesy 36g</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Crisps</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>8</v>
+      </c>
+      <c r="F21" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pom-Bear Original 19g</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Crisps</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>8</v>
+      </c>
+      <c r="F22" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kettle Lightly Salted 40g</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Crisps</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Grenade Carb Killa Cookie Dough 60g</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Protein/Health</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Grenade Carb Killa Oreo 60g</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Protein/Health</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Trek Protein Flapjack Cocoa Oat 50g</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Protein/Health</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Nakd Cocoa Delight 35g</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Protein/Health</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fulfil Chocolate &amp; Hazelnut 55g</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Protein/Health</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Barebells Protein Bar Salty Peanut 55g</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Protein/Health</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Optimum Nutrition Protein Shake Chocolate 330ml</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Protein/Health</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Grenade Protein Shake Chocolate Insanity 330ml</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Protein/Health</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Coca-Cola Original 330ml Can</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Cold Drinks</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Diet Coke 330ml Can</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Cold Drinks</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Fanta Orange 330ml Can</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Cold Drinks</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pepsi 330ml Can</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cold Drinks</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>7Up 330ml Can</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Cold Drinks</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Lucozade Original 380ml</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Cold Drinks</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>6</v>
+      </c>
+      <c r="F37" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Lipton Iced Tea Peach 330ml Can</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Cold Drinks</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>6</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Monster Energy 500ml Can</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Cold Drinks</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>6</v>
+      </c>
+      <c r="F39" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Red Bull 250ml Can</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Cold Drinks</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Oasis Citrus Punch 500ml</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Cold Drinks</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Highland Spring Still 500ml</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>6</v>
+      </c>
+      <c r="F42" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Evian 500ml</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Volvic 500ml</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>drinks-heavy (47 sel, 326 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Mars Bar 51g</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>10</v>
+      </c>
+      <c r="F46" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Snickers 48g</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>10</v>
+      </c>
+      <c r="F47" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>KitKat 4 Finger 41.5g</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>10</v>
+      </c>
+      <c r="F48" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Dairy Milk 45g</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>10</v>
+      </c>
+      <c r="F49" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Twirl 43g</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>10</v>
+      </c>
+      <c r="F50" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Maltesers 37g</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F51" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Walkers Cheese &amp; Onion Grab Bag 45g</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Crisps</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>8</v>
+      </c>
+      <c r="F52" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Walkers Ready Salted Grab Bag 45g</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Crisps</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" t="n">
+        <v>8</v>
+      </c>
+      <c r="F53" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>McCoy's Salt &amp; Vinegar Grab Bag 45g</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Crisps</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>8</v>
+      </c>
+      <c r="F54" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Doritos Chilli Heatwave 40g</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Crisps</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>8</v>
+      </c>
+      <c r="F55" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Wotsits Really Cheesy 36g</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Crisps</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>8</v>
+      </c>
+      <c r="F56" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Grenade Carb Killa Cookie Dough 60g</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Protein/Health</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>6</v>
+      </c>
+      <c r="F57" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Grenade Carb Killa Oreo 60g</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Protein/Health</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>6</v>
+      </c>
+      <c r="F58" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Trek Protein Flapjack Cocoa Oat 50g</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Protein/Health</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F59" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Fulfil Chocolate &amp; Hazelnut 55g</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Protein/Health</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>6</v>
+      </c>
+      <c r="F60" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Optimum Nutrition Protein Shake Chocolate 330ml</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Protein/Health</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>5</v>
+      </c>
+      <c r="F61" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Grenade Protein Shake Chocolate Insanity 330ml</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Protein/Health</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>5</v>
+      </c>
+      <c r="F62" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Coca-Cola Original 330ml Can</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Cold Drinks</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" t="n">
+        <v>6</v>
+      </c>
+      <c r="F63" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Diet Coke 330ml Can</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Cold Drinks</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" t="n">
+        <v>6</v>
+      </c>
+      <c r="F64" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Pepsi 330ml Can</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Cold Drinks</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" t="n">
+        <v>6</v>
+      </c>
+      <c r="F65" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Fanta Orange 330ml Can</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Cold Drinks</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" t="n">
+        <v>6</v>
+      </c>
+      <c r="F66" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>7Up 330ml Can</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Cold Drinks</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" t="n">
+        <v>6</v>
+      </c>
+      <c r="F67" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Lucozade Original 380ml</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Cold Drinks</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" t="n">
+        <v>6</v>
+      </c>
+      <c r="F68" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Lipton Iced Tea Peach 330ml Can</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Cold Drinks</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" t="n">
+        <v>6</v>
+      </c>
+      <c r="F69" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Monster Energy 500ml Can</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Cold Drinks</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" t="n">
+        <v>6</v>
+      </c>
+      <c r="F70" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Red Bull 250ml Can</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Cold Drinks</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" t="n">
+        <v>6</v>
+      </c>
+      <c r="F71" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Oasis Citrus Punch 500ml</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Cold Drinks</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" t="n">
+        <v>6</v>
+      </c>
+      <c r="F72" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Highland Spring Still 500ml</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" t="n">
+        <v>6</v>
+      </c>
+      <c r="F73" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Highland Spring Sparkling 500ml</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>6</v>
+      </c>
+      <c r="F74" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Evian 500ml</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>6</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2312,192 +4054,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Assumptions &amp; Spikes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Evidence or spike. SPIKE rows have an experiment in scratch/spikes/.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Spike</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Unblocks</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>spike.001</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Restock fill-level trigger threshold</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>config/policies.yaml#restock-trigger, tools/route.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>spike.002</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Default restock cadence per machine</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>config/cadence.yaml, config/workflows.yaml#weekly-route</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>spike.003</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Stockout-rate target</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>config/kpis.yaml#stockout_rate_pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>spike.004</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Cash variance tolerance</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>config/kpis.yaml#cash_variance_pct, config/policies.yaml#cash-investigate</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>spike.005</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Product add/cut rule</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>config/policies.yaml#product-cut</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>spike.006</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Target vends/day and machine-buy trigger</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>config/kpis.yaml#vends_per_machine_per_day, config/policies.yaml#machine-buy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>